--- a/testdata/TestData.xlsx
+++ b/testdata/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Farm2Me Live Project - Automation Testing\eclipse-workspace\Java_Automation\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B84E4A-74B2-4DDD-8D4D-086844A272BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE12735-5593-4ABE-9606-E5A45A6A6058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>Manjuurs@123</t>
   </si>
@@ -54,18 +54,28 @@
   </si>
   <si>
     <t>Valid</t>
+  </si>
+  <si>
+    <t>1234567890</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -97,12 +107,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -387,7 +400,7 @@
     <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -399,8 +412,8 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>1234567890</v>
+      <c r="A2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -410,8 +423,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>1234567890</v>
+      <c r="A3" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
